--- a/code/outputs/问题一/问题一_无储能基准_result1提交格式.xlsx
+++ b/code/outputs/问题一/问题一_无储能基准_result1提交格式.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="Rd55266741c00494f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="Re5d29389d1974599"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="R77b170f741b14003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="Ree1adc52cf594bcc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -774,8 +774,6 @@
   <x:cols>
     <x:col min="1" max="2" width="13.6328125" style="3" customWidth="1"/>
     <x:col min="3" max="16384" width="8.7265625" style="4" customWidth="0"/>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="14" customHeight="1">
@@ -1949,11 +1947,6 @@
   <x:cols>
     <x:col min="1" max="3" width="11.6328125" style="4" customWidth="1"/>
     <x:col min="4" max="16384" width="8.7265625" style="4" customWidth="0"/>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="5" customFormat="1" ht="14" customHeight="1">
